--- a/public/converted/nomenklatura-vg-treyd-schet-1295-31-10-v-zagruzku-1s.xlsx
+++ b/public/converted/nomenklatura-vg-treyd-schet-1295-31-10-v-zagruzku-1s.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$2:$H$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$2:$I$230</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -55,11 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -434,8 +435,9 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,10 +480,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>Вид номенклатуры</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Бренд</t>
         </is>
@@ -514,12 +521,15 @@
           <t>8516609000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G3" s="4" t="n">
+        <v>3562.2</v>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -549,12 +559,15 @@
           <t>8516609000</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G4" s="4" t="n">
+        <v>1240.2</v>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -587,12 +600,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G5" s="4" t="n">
+        <v>1726.2</v>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -622,12 +638,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G6" s="4" t="n">
+        <v>2464.2</v>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -657,12 +676,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G7" s="4" t="n">
+        <v>2950.2</v>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -695,12 +717,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G8" s="4" t="n">
+        <v>1492.2</v>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -733,12 +758,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G9" s="4" t="n">
+        <v>1384.2</v>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -764,12 +792,15 @@
         <v>1</v>
       </c>
       <c r="F10" s="3" t="n"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G10" s="4" t="n">
+        <v>1492.2</v>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -799,12 +830,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G11" s="4" t="n">
+        <v>2626.2</v>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -834,12 +868,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G12" s="4" t="n">
+        <v>2626.2</v>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -872,12 +909,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G13" s="4" t="n">
+        <v>2302.2</v>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -910,12 +950,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G14" s="4" t="n">
+        <v>1492.2</v>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -945,12 +988,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G15" s="4" t="n">
+        <v>2050.2</v>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -983,12 +1029,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G16" s="4" t="n">
+        <v>1654.2</v>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1018,12 +1067,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G17" s="4" t="n">
+        <v>1888.2</v>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1053,12 +1105,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G18" s="4" t="n">
+        <v>2950.2</v>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1091,12 +1146,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G19" s="4" t="n">
+        <v>2590.2</v>
       </c>
       <c r="H19" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1129,12 +1187,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G20" s="4" t="n">
+        <v>2626.2</v>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1167,12 +1228,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G21" s="4" t="n">
+        <v>1780.2</v>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1202,12 +1266,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G22" s="4" t="n">
+        <v>3112.2</v>
       </c>
       <c r="H22" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1233,12 +1300,15 @@
         <v>1</v>
       </c>
       <c r="F23" s="3" t="n"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G23" s="4" t="n">
+        <v>2199</v>
       </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Xiaomi</t>
         </is>
@@ -1271,12 +1341,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G24" s="4" t="n">
+        <v>1299</v>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>Xiaomi</t>
         </is>
@@ -1302,12 +1375,15 @@
         <v>1</v>
       </c>
       <c r="F25" s="3" t="n"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G25" s="4" t="n">
+        <v>1299</v>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Xiaomi</t>
         </is>
@@ -1340,12 +1416,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G26" s="4" t="n">
+        <v>2194.2</v>
       </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1378,12 +1457,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G27" s="4" t="n">
+        <v>700.2</v>
       </c>
       <c r="H27" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1416,12 +1498,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G28" s="4" t="n">
+        <v>556.2</v>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1454,12 +1539,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G29" s="4" t="n">
+        <v>736.2</v>
       </c>
       <c r="H29" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1489,12 +1577,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G30" s="4" t="n">
+        <v>808.2</v>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1527,12 +1618,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G31" s="4" t="n">
+        <v>628.2</v>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1562,12 +1656,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G32" s="4" t="n">
+        <v>1384.2</v>
       </c>
       <c r="H32" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1600,12 +1697,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G33" s="4" t="n">
+        <v>646.2</v>
       </c>
       <c r="H33" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1638,12 +1738,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G34" s="4" t="n">
+        <v>646.2</v>
       </c>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1676,12 +1779,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G35" s="4" t="n">
+        <v>898.2</v>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1714,12 +1820,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G36" s="4" t="n">
+        <v>970.2</v>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1752,12 +1861,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G37" s="4" t="n">
+        <v>898.2</v>
       </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1790,12 +1902,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G38" s="4" t="n">
+        <v>808.2</v>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1828,12 +1943,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G39" s="4" t="n">
+        <v>1618.2</v>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1866,12 +1984,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G40" s="4" t="n">
+        <v>2104.2</v>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1904,12 +2025,15 @@
           <t>8414510000</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G41" s="4" t="n">
+        <v>808.2</v>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1942,12 +2066,15 @@
           <t>8414510000</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G42" s="4" t="n">
+        <v>1060.2</v>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -1980,12 +2107,15 @@
           <t>8414510000</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G43" s="4" t="n">
+        <v>574.2</v>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2018,12 +2148,15 @@
           <t>8414510000</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G44" s="4" t="n">
+        <v>574.2</v>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2056,12 +2189,15 @@
           <t>8414510000</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G45" s="4" t="n">
+        <v>736.2</v>
       </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2094,12 +2230,15 @@
           <t>8414510000</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G46" s="4" t="n">
+        <v>1132.2</v>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2132,12 +2271,15 @@
           <t>8414510000</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G47" s="4" t="n">
+        <v>1294.2</v>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2170,12 +2312,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G48" s="4" t="n">
+        <v>2914.2</v>
       </c>
       <c r="H48" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2208,12 +2353,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G49" s="4" t="n">
+        <v>3724.2</v>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2246,12 +2394,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G50" s="4" t="n">
+        <v>4048.2</v>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2284,12 +2435,15 @@
           <t>8508190009</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G51" s="4" t="n">
+        <v>6802.2</v>
       </c>
       <c r="H51" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2322,12 +2476,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G52" s="4" t="n">
+        <v>5020.2</v>
       </c>
       <c r="H52" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2360,12 +2517,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G53" s="4" t="n">
+        <v>3886.2</v>
       </c>
       <c r="H53" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2398,12 +2558,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G54" s="4" t="n">
+        <v>3886.2</v>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2429,12 +2592,15 @@
         <v>1</v>
       </c>
       <c r="F55" s="3" t="n"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G55" s="4" t="n">
+        <v>4372.2</v>
       </c>
       <c r="H55" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2467,12 +2633,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G56" s="4" t="n">
+        <v>3562.2</v>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2505,12 +2674,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G57" s="4" t="n">
+        <v>3562.2</v>
       </c>
       <c r="H57" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2543,12 +2715,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G58" s="4" t="n">
+        <v>2104.2</v>
       </c>
       <c r="H58" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2581,12 +2756,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G59" s="4" t="n">
+        <v>2428.2</v>
       </c>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2619,12 +2797,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G60" s="4" t="n">
+        <v>2752.2</v>
       </c>
       <c r="H60" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2657,12 +2838,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G61" s="4" t="n">
+        <v>3400.2</v>
       </c>
       <c r="H61" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2695,12 +2879,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G62" s="4" t="n">
+        <v>3400.2</v>
       </c>
       <c r="H62" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2733,12 +2920,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G63" s="4" t="n">
+        <v>3886.2</v>
       </c>
       <c r="H63" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2771,12 +2961,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G64" s="4" t="n">
+        <v>3886.2</v>
       </c>
       <c r="H64" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2809,12 +3002,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G65" s="4" t="n">
+        <v>5182.2</v>
       </c>
       <c r="H65" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2847,12 +3043,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G66" s="4" t="n">
+        <v>2428.2</v>
       </c>
       <c r="H66" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2882,12 +3081,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G67" s="4" t="n">
+        <v>3886.2</v>
       </c>
       <c r="H67" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2920,12 +3122,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G68" s="4" t="n">
+        <v>3724.2</v>
       </c>
       <c r="H68" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2958,12 +3163,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G69" s="4" t="n">
+        <v>3886.2</v>
       </c>
       <c r="H69" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -2996,12 +3204,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G70" s="4" t="n">
+        <v>2104.2</v>
       </c>
       <c r="H70" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3034,12 +3245,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G71" s="4" t="n">
+        <v>6154.2</v>
       </c>
       <c r="H71" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3072,12 +3286,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G72" s="4" t="n">
+        <v>4858.2</v>
       </c>
       <c r="H72" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3110,12 +3327,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G73" s="4" t="n">
+        <v>2266.2</v>
       </c>
       <c r="H73" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3148,12 +3368,15 @@
           <t>9506911000</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G74" s="4" t="n">
+        <v>1186.2</v>
       </c>
       <c r="H74" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3186,12 +3409,15 @@
           <t>8516108000</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G75" s="4" t="n">
+        <v>719</v>
       </c>
       <c r="H75" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3224,12 +3450,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G76" s="4" t="n">
+        <v>1699</v>
       </c>
       <c r="H76" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3262,12 +3491,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G77" s="4" t="n">
+        <v>949</v>
       </c>
       <c r="H77" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3300,12 +3532,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G78" s="4" t="n">
+        <v>999</v>
       </c>
       <c r="H78" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3338,12 +3573,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G79" s="4" t="n">
+        <v>999</v>
       </c>
       <c r="H79" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3376,12 +3614,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G80" s="4" t="n">
+        <v>2199</v>
       </c>
       <c r="H80" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3414,12 +3655,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G81" s="4" t="n">
+        <v>599</v>
       </c>
       <c r="H81" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3452,12 +3696,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G82" s="4" t="n">
+        <v>549</v>
       </c>
       <c r="H82" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3490,12 +3737,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G83" s="4" t="n">
+        <v>599</v>
       </c>
       <c r="H83" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3528,12 +3778,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G84" s="4" t="n">
+        <v>599</v>
       </c>
       <c r="H84" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3566,12 +3819,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G85" s="4" t="n">
+        <v>699</v>
       </c>
       <c r="H85" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3604,12 +3860,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G86" s="4" t="n">
+        <v>1199</v>
       </c>
       <c r="H86" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3642,12 +3901,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G87" s="4" t="n">
+        <v>899</v>
       </c>
       <c r="H87" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3680,12 +3942,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G88" s="4" t="n">
+        <v>899</v>
       </c>
       <c r="H88" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3718,12 +3983,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G89" s="4" t="n">
+        <v>1399</v>
       </c>
       <c r="H89" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3756,12 +4024,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G90" s="4" t="n">
+        <v>899</v>
       </c>
       <c r="H90" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3794,12 +4065,15 @@
           <t>8414600001</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G91" s="4" t="n">
+        <v>1299</v>
       </c>
       <c r="H91" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3832,12 +4106,15 @@
           <t>7321119000</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G92" s="4" t="n">
+        <v>999</v>
       </c>
       <c r="H92" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3870,12 +4147,15 @@
           <t>7323999100</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G93" s="4" t="n">
+        <v>790.2</v>
       </c>
       <c r="H93" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3908,12 +4188,15 @@
           <t>8451300000</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G94" s="4" t="n">
+        <v>808.2</v>
       </c>
       <c r="H94" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3946,12 +4229,15 @@
           <t>8451300000</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G95" s="4" t="n">
+        <v>1222.2</v>
       </c>
       <c r="H95" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -3984,12 +4270,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G96" s="4" t="n">
+        <v>1132.2</v>
       </c>
       <c r="H96" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4022,12 +4311,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G97" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H97" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4060,12 +4352,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G98" s="4" t="n">
+        <v>2752.2</v>
       </c>
       <c r="H98" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4098,12 +4393,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G99" s="4" t="n">
+        <v>3724.2</v>
       </c>
       <c r="H99" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4136,12 +4434,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G100" s="4" t="n">
+        <v>3238.2</v>
       </c>
       <c r="H100" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4174,12 +4475,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G101" s="4" t="n">
+        <v>4462.2</v>
       </c>
       <c r="H101" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4212,12 +4516,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G102" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H102" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4250,12 +4557,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G103" s="4" t="n">
+        <v>4858.2</v>
       </c>
       <c r="H103" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4288,12 +4598,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G104" s="4" t="n">
+        <v>3886.2</v>
       </c>
       <c r="H104" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4326,12 +4639,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G105" s="4" t="n">
+        <v>5830.2</v>
       </c>
       <c r="H105" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4357,12 +4673,15 @@
         <v>1</v>
       </c>
       <c r="F106" s="3" t="n"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G106" s="4" t="n">
+        <v>4372.2</v>
       </c>
       <c r="H106" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4395,12 +4714,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G107" s="4" t="n">
+        <v>2752.2</v>
       </c>
       <c r="H107" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4433,12 +4755,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G108" s="4" t="n">
+        <v>3562.2</v>
       </c>
       <c r="H108" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4471,12 +4796,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G109" s="4" t="n">
+        <v>4534.2</v>
       </c>
       <c r="H109" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4509,12 +4837,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G110" s="4" t="n">
+        <v>1499</v>
       </c>
       <c r="H110" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4547,12 +4878,15 @@
           <t>8516605000</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G111" s="4" t="n">
+        <v>718.2</v>
       </c>
       <c r="H111" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4585,12 +4919,15 @@
           <t>8516605000</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G112" s="4" t="n">
+        <v>1618.2</v>
       </c>
       <c r="H112" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4616,12 +4953,15 @@
         <v>1</v>
       </c>
       <c r="F113" s="3" t="n"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G113" s="4" t="n">
+        <v>862.2</v>
       </c>
       <c r="H113" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4654,12 +4994,15 @@
           <t>8516295000</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G114" s="4" t="n">
+        <v>1168.2</v>
       </c>
       <c r="H114" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4692,12 +5035,15 @@
           <t>8516295000</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G115" s="4" t="n">
+        <v>1294.2</v>
       </c>
       <c r="H115" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4730,12 +5076,15 @@
           <t>8516295000</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G116" s="4" t="n">
+        <v>1456.2</v>
       </c>
       <c r="H116" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4768,12 +5117,15 @@
           <t>8516295000</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G117" s="4" t="n">
+        <v>1060.2</v>
       </c>
       <c r="H117" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4806,12 +5158,15 @@
           <t>8516295000</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G118" s="4" t="n">
+        <v>1006.2</v>
       </c>
       <c r="H118" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4844,12 +5199,15 @@
           <t>8516295000</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G119" s="4" t="n">
+        <v>1168.2</v>
       </c>
       <c r="H119" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4882,12 +5240,15 @@
           <t>8516295000</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G120" s="4" t="n">
+        <v>1222.2</v>
       </c>
       <c r="H120" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4917,12 +5278,15 @@
           <t>8516295000</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G121" s="4" t="n">
+        <v>736.2</v>
       </c>
       <c r="H121" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4948,12 +5312,15 @@
         <v>1</v>
       </c>
       <c r="F122" s="3" t="n"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G122" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H122" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -4986,12 +5353,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G123" s="4" t="n">
+        <v>1870.2</v>
       </c>
       <c r="H123" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5024,12 +5394,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G124" s="4" t="n">
+        <v>2914.2</v>
       </c>
       <c r="H124" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5062,12 +5435,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G125" s="4" t="n">
+        <v>2914.2</v>
       </c>
       <c r="H125" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5100,12 +5476,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G126" s="4" t="n">
+        <v>4318.2</v>
       </c>
       <c r="H126" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5138,12 +5517,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G127" s="4" t="n">
+        <v>5992.2</v>
       </c>
       <c r="H127" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5173,12 +5555,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G128" s="4" t="n">
+        <v>6154.2</v>
       </c>
       <c r="H128" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5208,12 +5593,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G129" s="4" t="n">
+        <v>6154.2</v>
       </c>
       <c r="H129" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5243,12 +5631,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G130" s="4" t="n">
+        <v>6478.2</v>
       </c>
       <c r="H130" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5281,12 +5672,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G131" s="4" t="n">
+        <v>5758.2</v>
       </c>
       <c r="H131" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5319,12 +5713,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G132" s="4" t="n">
+        <v>8908.200000000001</v>
       </c>
       <c r="H132" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5357,12 +5754,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G133" s="4" t="n">
+        <v>7828.2</v>
       </c>
       <c r="H133" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5395,12 +5795,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G134" s="4" t="n">
+        <v>7774.2</v>
       </c>
       <c r="H134" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5433,12 +5836,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G135" s="4" t="n">
+        <v>10528.2</v>
       </c>
       <c r="H135" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5464,12 +5870,15 @@
         <v>1</v>
       </c>
       <c r="F136" s="3" t="n"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G136" s="4" t="n">
+        <v>9070.200000000001</v>
       </c>
       <c r="H136" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5502,12 +5911,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G137" s="4" t="n">
+        <v>10528.2</v>
       </c>
       <c r="H137" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5540,12 +5952,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G138" s="4" t="n">
+        <v>8098.2</v>
       </c>
       <c r="H138" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5578,12 +5993,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G139" s="4" t="n">
+        <v>10528.2</v>
       </c>
       <c r="H139" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5613,12 +6031,15 @@
           <t>8516710000</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G140" s="4" t="n">
+        <v>9394.200000000001</v>
       </c>
       <c r="H140" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5651,12 +6072,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G141" s="4" t="n">
+        <v>3724.2</v>
       </c>
       <c r="H141" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5689,12 +6113,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G142" s="4" t="n">
+        <v>3724.2</v>
       </c>
       <c r="H142" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5727,12 +6154,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G143" s="4" t="n">
+        <v>4048.2</v>
       </c>
       <c r="H143" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5765,12 +6195,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G144" s="4" t="n">
+        <v>4048.2</v>
       </c>
       <c r="H144" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5803,12 +6236,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G145" s="4" t="n">
+        <v>4372.2</v>
       </c>
       <c r="H145" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5841,12 +6277,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G146" s="4" t="n">
+        <v>5344.2</v>
       </c>
       <c r="H146" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5879,12 +6318,15 @@
           <t>9019109009</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G147" s="4" t="n">
+        <v>1618.2</v>
       </c>
       <c r="H147" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5910,12 +6352,15 @@
         <v>1</v>
       </c>
       <c r="F148" s="3" t="n"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G148" s="4" t="n">
+        <v>484.2</v>
       </c>
       <c r="H148" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5948,12 +6393,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G149" s="4" t="n">
+        <v>1989</v>
       </c>
       <c r="H149" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -5986,12 +6434,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G150" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H150" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6024,12 +6475,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G151" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H151" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6055,12 +6509,15 @@
         <v>1</v>
       </c>
       <c r="F152" s="3" t="n"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G152" s="4" t="n">
+        <v>1870.2</v>
       </c>
       <c r="H152" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6093,12 +6550,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G153" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H153" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6131,12 +6591,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G154" s="4" t="n">
+        <v>1870.2</v>
       </c>
       <c r="H154" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6169,12 +6632,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G155" s="4" t="n">
+        <v>1600.2</v>
       </c>
       <c r="H155" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6207,12 +6673,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G156" s="4" t="n">
+        <v>1600.2</v>
       </c>
       <c r="H156" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6245,12 +6714,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G157" s="4" t="n">
+        <v>1600.2</v>
       </c>
       <c r="H157" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6283,12 +6755,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G158" s="4" t="n">
+        <v>1600.2</v>
       </c>
       <c r="H158" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6321,12 +6796,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G159" s="4" t="n">
+        <v>1600.2</v>
       </c>
       <c r="H159" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6359,12 +6837,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G160" s="4" t="n">
+        <v>1600.2</v>
       </c>
       <c r="H160" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6390,12 +6871,15 @@
         <v>1</v>
       </c>
       <c r="F161" s="3" t="n"/>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G161" s="4" t="n">
+        <v>1600.2</v>
       </c>
       <c r="H161" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6428,12 +6912,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G162" s="4" t="n">
+        <v>2104.2</v>
       </c>
       <c r="H162" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6466,12 +6953,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G163" s="4" t="n">
+        <v>1870.2</v>
       </c>
       <c r="H163" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6504,12 +6994,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G164" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H164" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6542,12 +7035,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G165" s="4" t="n">
+        <v>1780.2</v>
       </c>
       <c r="H165" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6580,12 +7076,15 @@
           <t>8516500000</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G166" s="4" t="n">
+        <v>1456.2</v>
       </c>
       <c r="H166" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6618,12 +7117,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G167" s="4" t="n">
+        <v>1618.2</v>
       </c>
       <c r="H167" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6656,12 +7158,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G168" s="4" t="n">
+        <v>1618.2</v>
       </c>
       <c r="H168" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6694,12 +7199,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G169" s="4" t="n">
+        <v>2104.2</v>
       </c>
       <c r="H169" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6732,12 +7240,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G170" s="4" t="n">
+        <v>2590.2</v>
       </c>
       <c r="H170" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6770,12 +7281,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G171" s="4" t="n">
+        <v>2572.2</v>
       </c>
       <c r="H171" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6808,12 +7322,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G172" s="4" t="n">
+        <v>2590.2</v>
       </c>
       <c r="H172" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6846,12 +7363,15 @@
           <t>8516609000</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G173" s="4" t="n">
+        <v>718.2</v>
       </c>
       <c r="H173" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6884,12 +7404,15 @@
           <t>8516609000</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G174" s="4" t="n">
+        <v>1348.2</v>
       </c>
       <c r="H174" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6922,12 +7445,15 @@
           <t>8516609000</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G175" s="4" t="n">
+        <v>1888.2</v>
       </c>
       <c r="H175" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6960,12 +7486,15 @@
           <t>8516609000</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G176" s="4" t="n">
+        <v>1780.2</v>
       </c>
       <c r="H176" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -6998,12 +7527,15 @@
           <t>8516609000</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G177" s="4" t="n">
+        <v>2194.2</v>
       </c>
       <c r="H177" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7029,12 +7561,15 @@
         <v>1</v>
       </c>
       <c r="F178" s="3" t="n"/>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G178" s="4" t="n">
+        <v>1499</v>
       </c>
       <c r="H178" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7060,12 +7595,15 @@
         <v>1</v>
       </c>
       <c r="F179" s="3" t="n"/>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G179" s="4" t="n">
+        <v>1169</v>
       </c>
       <c r="H179" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7098,12 +7636,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G180" s="4" t="n">
+        <v>1294.2</v>
       </c>
       <c r="H180" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7136,12 +7677,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G181" s="4" t="n">
+        <v>1294.2</v>
       </c>
       <c r="H181" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7174,12 +7718,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G182" s="4" t="n">
+        <v>1618.2</v>
       </c>
       <c r="H182" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7205,12 +7752,15 @@
         <v>1</v>
       </c>
       <c r="F183" s="3" t="n"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G183" s="4" t="n">
+        <v>1618.2</v>
       </c>
       <c r="H183" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7243,12 +7793,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G184" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H184" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7281,12 +7834,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G185" s="4" t="n">
+        <v>2752.2</v>
       </c>
       <c r="H185" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7312,12 +7868,15 @@
         <v>1</v>
       </c>
       <c r="F186" s="3" t="n"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G186" s="4" t="n">
+        <v>1329</v>
       </c>
       <c r="H186" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7343,12 +7902,15 @@
         <v>1</v>
       </c>
       <c r="F187" s="3" t="n"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G187" s="4" t="n">
+        <v>899</v>
       </c>
       <c r="H187" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7381,12 +7943,15 @@
           <t>8516605000</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G188" s="4" t="n">
+        <v>1649</v>
       </c>
       <c r="H188" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7419,12 +7984,15 @@
           <t>8516605000</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G189" s="4" t="n">
+        <v>2699</v>
       </c>
       <c r="H189" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7457,12 +8025,15 @@
           <t>8516605000</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G190" s="4" t="n">
+        <v>849</v>
       </c>
       <c r="H190" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7495,12 +8066,15 @@
           <t>8516605000</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G191" s="4" t="n">
+        <v>799</v>
       </c>
       <c r="H191" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7533,12 +8107,15 @@
           <t>8516605000</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G192" s="4" t="n">
+        <v>1299</v>
       </c>
       <c r="H192" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7571,12 +8148,15 @@
           <t>8508190001</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G193" s="4" t="n">
+        <v>1618.2</v>
       </c>
       <c r="H193" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7609,12 +8189,15 @@
           <t>8508110000</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G194" s="4" t="n">
+        <v>2590.2</v>
       </c>
       <c r="H194" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7647,12 +8230,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G195" s="4" t="n">
+        <v>1132.2</v>
       </c>
       <c r="H195" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7685,12 +8271,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G196" s="4" t="n">
+        <v>1384.2</v>
       </c>
       <c r="H196" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7720,12 +8309,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G197" s="4" t="n">
+        <v>2032.2</v>
       </c>
       <c r="H197" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7758,12 +8350,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G198" s="4" t="n">
+        <v>2032.2</v>
       </c>
       <c r="H198" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7796,12 +8391,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G199" s="4" t="n">
+        <v>1708.2</v>
       </c>
       <c r="H199" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7834,12 +8432,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G200" s="4" t="n">
+        <v>1780.2</v>
       </c>
       <c r="H200" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7872,12 +8473,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G201" s="4" t="n">
+        <v>1780.2</v>
       </c>
       <c r="H201" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7910,12 +8514,15 @@
           <t>8516108000</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G202" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H202" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7948,12 +8555,15 @@
           <t>8516108000</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G203" s="4" t="n">
+        <v>1942.2</v>
       </c>
       <c r="H203" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -7986,12 +8596,15 @@
           <t>8516108000</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G204" s="4" t="n">
+        <v>2032.2</v>
       </c>
       <c r="H204" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8024,12 +8637,15 @@
           <t>8516108000</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G205" s="4" t="n">
+        <v>2032.2</v>
       </c>
       <c r="H205" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8059,12 +8675,15 @@
           <t>8516108000</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G206" s="4" t="n">
+        <v>2104.2</v>
       </c>
       <c r="H206" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8097,12 +8716,15 @@
           <t>9603909100</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G207" s="4" t="n">
+        <v>628.2</v>
       </c>
       <c r="H207" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8135,12 +8757,15 @@
           <t>8516310009</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G208" s="4" t="n">
+        <v>2428.2</v>
       </c>
       <c r="H208" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8173,12 +8798,15 @@
           <t>8516310009</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G209" s="4" t="n">
+        <v>1546.2</v>
       </c>
       <c r="H209" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8211,12 +8839,15 @@
           <t>8516310009</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G210" s="4" t="n">
+        <v>1546.2</v>
       </c>
       <c r="H210" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8249,12 +8880,15 @@
           <t>8516108000</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G211" s="4" t="n">
+        <v>484.2</v>
       </c>
       <c r="H211" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8287,12 +8921,15 @@
           <t>8516108000</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G212" s="4" t="n">
+        <v>484.2</v>
       </c>
       <c r="H212" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8325,12 +8962,15 @@
           <t>8516108000</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G213" s="4" t="n">
+        <v>484.2</v>
       </c>
       <c r="H213" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8363,12 +9003,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G214" s="4" t="n">
+        <v>736.2</v>
       </c>
       <c r="H214" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8401,12 +9044,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G215" s="4" t="n">
+        <v>736.2</v>
       </c>
       <c r="H215" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8436,12 +9082,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G216" s="4" t="n">
+        <v>430.2</v>
       </c>
       <c r="H216" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8474,12 +9123,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G217" s="4" t="n">
+        <v>412.2</v>
       </c>
       <c r="H217" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8512,12 +9164,15 @@
           <t>8516797000</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G218" s="4" t="n">
+        <v>610.2</v>
       </c>
       <c r="H218" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8550,12 +9205,15 @@
           <t>9603909100</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G219" s="4" t="n">
+        <v>124.2</v>
       </c>
       <c r="H219" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8585,12 +9243,15 @@
           <t>9603909100</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G220" s="4" t="n">
+        <v>448.2</v>
       </c>
       <c r="H220" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8623,12 +9284,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G221" s="4" t="n">
+        <v>628.2</v>
       </c>
       <c r="H221" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8658,12 +9322,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G222" s="4" t="n">
+        <v>898.2</v>
       </c>
       <c r="H222" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8696,12 +9363,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G223" s="4" t="n">
+        <v>970.2</v>
       </c>
       <c r="H223" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8734,12 +9404,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G224" s="4" t="n">
+        <v>2428.2</v>
       </c>
       <c r="H224" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8772,12 +9445,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G225" s="4" t="n">
+        <v>1294.2</v>
       </c>
       <c r="H225" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8810,12 +9486,15 @@
           <t>8509400000</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G226" s="4" t="n">
+        <v>2104.2</v>
       </c>
       <c r="H226" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8848,12 +9527,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G227" s="4" t="n">
+        <v>1132.2</v>
       </c>
       <c r="H227" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8886,12 +9568,15 @@
           <t>8516607000</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G228" s="4" t="n">
+        <v>538.2</v>
       </c>
       <c r="H228" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8924,12 +9609,15 @@
           <t>8516299900</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G229" s="4" t="n">
+        <v>1309</v>
       </c>
       <c r="H229" t="inlineStr">
+        <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
         <is>
           <t>Weissgauff</t>
         </is>
@@ -8962,19 +9650,22 @@
           <t>8516299900</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
+      <c r="G230" s="4" t="n">
+        <v>899</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
+          <t>Товары</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
           <t>Weissgauff</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H230"/>
+  <autoFilter ref="A2:I230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>